--- a/Result/profitability/6170.xlsx
+++ b/Result/profitability/6170.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0175</v>
+        <v>1.09125</v>
       </c>
       <c r="N2" t="n">
-        <v>28.76875</v>
+        <v>29.34125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03625</v>
+        <v>0.99125</v>
       </c>
       <c r="N3" t="n">
-        <v>26.61625</v>
+        <v>27.1175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0.96</v>
+        <v>0.9737500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>24.23375</v>
+        <v>24.51625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8387500000000001</v>
+        <v>0.87625</v>
       </c>
       <c r="N5" t="n">
-        <v>21.4175</v>
+        <v>21.805</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7675</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>19.19625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5725</v>
+        <v>0.57125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.03</v>
+        <v>16.3925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45875</v>
+        <v>0.46</v>
       </c>
       <c r="N8" t="n">
-        <v>13.37375</v>
+        <v>13.7025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.1675</v>
       </c>
       <c r="N10" t="n">
-        <v>9.803750000000001</v>
+        <v>9.803749999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.03125000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>9.690000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.04000000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9.72125</v>
+        <v>9.721250000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>765</v>
+      </c>
+      <c r="D75" t="n">
+        <v>507</v>
+      </c>
+      <c r="E75" t="n">
+        <v>258</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>79</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>54</v>
+      </c>
+      <c r="J75" t="n">
+        <v>134</v>
+      </c>
+      <c r="K75" t="n">
+        <v>107</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.11875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.00917431192660545</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08451156812339322</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1011419249592169</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
